--- a/submissions/2A202602777_NguyenThanhBinh/results.xlsx
+++ b/submissions/2A202602777_NguyenThanhBinh/results.xlsx
@@ -16,13 +16,13 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Backbones'!$A$1:$A$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Training'!$A$1:$A$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Inference'!$A$1:$A$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Backbones'!$A$1:$O$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Training'!$A$1:$M$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Inference'!$A$1:$M$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Final'!$A$1:$A$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'PerClass'!$A$1:$A$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Latency'!$A$1:$J$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Summary'!$A$1:$A$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Latency'!$A$1:$J$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Summary'!$A$1:$H$11</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -30,7 +30,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0000"/>
+  </numFmts>
   <fonts count="3">
     <font>
       <name val="Calibri"/>
@@ -41,13 +43,13 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
     </font>
     <font>
       <b val="1"/>
+      <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -57,6 +59,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="0017324D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DCFCE7"/>
       </patternFill>
     </fill>
   </fills>
@@ -78,12 +85,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -449,17 +459,390 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:O6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="17" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="13" max="13"/>
+    <col width="15" customWidth="1" min="14" max="14"/>
+    <col width="15" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="n"/>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>exp_id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>backbone</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>pretrained tag</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>params (M)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>GMAC (estimated)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>resolution</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>epochs</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>seed</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>train DataParallel</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>macro-F1 val</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>top-1 val</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>train sec/epoch</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>latency p50 batch1 (ms)</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>latency GPU</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>B01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>resnet50</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>a1_in1k</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>23.526473</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>4.087154688</v>
+      </c>
+      <c r="F2" t="n">
+        <v>224</v>
+      </c>
+      <c r="G2" t="n">
+        <v>12</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="b">
+        <v>1</v>
+      </c>
+      <c r="J2" s="2" t="n">
+        <v>0.8213613683514545</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>0.8663239074550129</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>127.23353804175</v>
+      </c>
+      <c r="M2" s="2" t="n">
+        <v>6.217055499973867</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Tesla T4</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Conv2d + Linear + attention QK/AV MACs; excludes norm/activation/pooling</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>B02</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>resnext50_32x4d</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>a1h_in1k</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>22.998345</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>4.228450304</v>
+      </c>
+      <c r="F3" t="n">
+        <v>224</v>
+      </c>
+      <c r="G3" t="n">
+        <v>12</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="b">
+        <v>1</v>
+      </c>
+      <c r="J3" s="2" t="n">
+        <v>0.7654423267945519</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>0.8189088831762353</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>89.91016572374993</v>
+      </c>
+      <c r="M3" s="2" t="n">
+        <v>9.234667000100671</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Tesla T4</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Conv2d + Linear + attention QK/AV MACs; excludes norm/activation/pooling</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>B03</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>convnext_tiny</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>in12k_ft_in1k</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>27.827049</v>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>4.454770176</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>224</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" s="4" t="n">
+        <v>0.9673897763576167</v>
+      </c>
+      <c r="K4" s="4" t="n">
+        <v>0.9754355898314767</v>
+      </c>
+      <c r="L4" s="4" t="n">
+        <v>89.76344590600009</v>
+      </c>
+      <c r="M4" s="4" t="n">
+        <v>5.602968000403052</v>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>Tesla T4</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
+          <t>Conv2d + Linear + attention QK/AV MACs; excludes norm/activation/pooling</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>B04</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>deit_small_patch16_224</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>fb_in1k</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>21.669129</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>4.59850176</v>
+      </c>
+      <c r="F5" t="n">
+        <v>224</v>
+      </c>
+      <c r="G5" t="n">
+        <v>12</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="b">
+        <v>1</v>
+      </c>
+      <c r="J5" s="2" t="n">
+        <v>0.9517523607647651</v>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>0.9640102827763496</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>77.37625700308331</v>
+      </c>
+      <c r="M5" s="2" t="n">
+        <v>5.309799499627843</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Tesla T4</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Conv2d + Linear + attention QK/AV MACs; excludes norm/activation/pooling</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>B05</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>efficientnet_b0</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>ra_in1k</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>4.019077</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>0.384546272</v>
+      </c>
+      <c r="F6" t="n">
+        <v>224</v>
+      </c>
+      <c r="G6" t="n">
+        <v>12</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" s="2" t="n">
+        <v>0.8316023339484606</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>0.8706083976006855</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>83.56513903349999</v>
+      </c>
+      <c r="M6" s="2" t="n">
+        <v>7.551150499693904</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Tesla T4</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Conv2d + Linear + attention QK/AV MACs; excludes norm/activation/pooling</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:A1"/>
+  <autoFilter ref="A1:O6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -470,17 +853,720 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:M12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="n"/>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>exp_id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>backbone</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>axis</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>changed from T00</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>seed</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>macro-F1 val</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>top-1 val</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>delta vs T00</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>train sec/epoch</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>init</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>augmentation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>T00</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>convnext_tiny</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>0.9673897763576167</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>0.9754355898314767</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>88.89748331024983</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>finetune</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>basic</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>ce</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>T01</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>convnext_tiny</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>A: init=scratch</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>A: init=scratch</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>0.3626660135482351</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>0.5855469865752642</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>-0.6047237628093816</v>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>89.81464335508342</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>scratch</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>basic</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>ce</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>A: init=scratch</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>T02</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>convnext_tiny</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>A: init=frozen</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>A: init=frozen</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>0.8554060363945696</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>0.8840331333904599</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>-0.1119837399630471</v>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>58.93685513866664</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>frozen</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>basic</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>ce</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>A: init=frozen</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>T03</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>convnext_tiny</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>B: color jitter</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>B: color jitter</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>0.9654433427353758</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>0.9728648957440731</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>-0.001946433622240895</v>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>132.5836761094166</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>finetune</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>color</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>ce</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>B: color jitter</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>T04</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>convnext_tiny</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>B: Mixup</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>B: Mixup</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>0.9755872966432046</v>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>0.9811482433590403</v>
+      </c>
+      <c r="H6" s="4" t="n">
+        <v>0.008197520285587956</v>
+      </c>
+      <c r="I6" s="4" t="n">
+        <v>87.04003270566682</v>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>finetune</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>basic</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>ce</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>B: Mixup</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>T05</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>convnext_tiny</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>B: CutMix</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>B: CutMix</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>0.9723768356135333</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>0.9791488146243931</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>0.004987059255916582</v>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>87.18019424083361</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>finetune</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>basic</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>ce</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>B: CutMix</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>T06</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>convnext_tiny</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>C: label smoothing 0.1</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>C: label smoothing 0.1</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>0.9672586196214445</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>0.974293059125964</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>-0.0001311567361721444</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>83.82033239316677</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>finetune</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>basic</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>ls</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>C: label smoothing 0.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>T07</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>convnext_tiny</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>C: focal gamma 2</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>C: focal gamma 2</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>0.96387291544636</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>0.9725792630676949</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>-0.003516860911256692</v>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>82.83924139425001</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>finetune</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>basic</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>focal</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>C: focal gamma 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>T08</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>convnext_tiny</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>C: class-weighted CE</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>C: class-weighted CE</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>0.9611829332919037</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>0.9708654670094259</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>-0.006206843065712953</v>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>85.4939234857499</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>finetune</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>basic</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>ce_weighted</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>C: class-weighted CE</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>T09</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>convnext_tiny</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>F: EMA 0.999</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>F: EMA 0.999</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>0.9713766851027318</v>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>0.9785775492716366</v>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>0.003986908745115092</v>
+      </c>
+      <c r="I11" s="2" t="n">
+        <v>87.38035820858356</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>finetune</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>basic</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>ce</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>F: EMA 0.999</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>T10</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>convnext_tiny</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>B+C combination: T04+T06 (chosen on val; may not improve baseline)</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>B+C combination: T04+T06 (chosen on val; may not improve baseline)</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>0.9688417362275819</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>0.9768637532133676</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>0.001451959869965158</v>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>84.69132408224959</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>finetune</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>basic</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>ls</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>B+C combination: T04+T06 (chosen on val; may not improve baseline)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:A1"/>
+  <autoFilter ref="A1:M12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -491,17 +1577,387 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="9" max="9"/>
+    <col width="17" customWidth="1" min="10" max="10"/>
+    <col width="27" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="n"/>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>exp_id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>method</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>checkpoint</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>K views</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>macro-F1 val</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>top-1 val</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ECE val</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>p50 batch1 (ms)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>p95 batch1 (ms)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>p99 batch1 (ms)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>throughput batch1 (img/s)</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>relative cost vs I00</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>I00</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>single view</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>/kaggle/working/day2_output/runs/T04/seed0/checkpoint_best.pt</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>0.9755872966432046</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>0.9811482433590403</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>0.02047231015359558</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>5.810885999380844</v>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>8.823867600040103</v>
+      </c>
+      <c r="J2" s="2" t="n">
+        <v>8.951247469703958</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>172.0907964992862</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>base resize/decode/H2D excluded; actual TTA, aggregation included</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>I01</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>horizontal flip, mean probabilities</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>/kaggle/working/day2_output/runs/T04/seed0/checkpoint_best.pt</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>0.9775449072463195</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>0.9828620394173093</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>0.0212183539542563</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>11.09968849959841</v>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>11.78108184867597</v>
+      </c>
+      <c r="J3" s="2" t="n">
+        <v>12.46520792930823</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>90.09261836818033</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>1.910154234789858</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>base resize/decode/H2D excluded; actual TTA, aggregation included</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>I02</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>five crops, mean probabilities</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>/kaggle/working/day2_output/runs/T04/seed0/checkpoint_best.pt</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>0.9780877838742277</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>0.9840045701228221</v>
+      </c>
+      <c r="G4" s="4" t="n">
+        <v>0.03909269905675995</v>
+      </c>
+      <c r="H4" s="4" t="n">
+        <v>27.3083680003765</v>
+      </c>
+      <c r="I4" s="4" t="n">
+        <v>28.39989105013956</v>
+      </c>
+      <c r="J4" s="4" t="n">
+        <v>29.39391268009785</v>
+      </c>
+      <c r="K4" s="4" t="n">
+        <v>36.61881222584275</v>
+      </c>
+      <c r="L4" s="4" t="n">
+        <v>4.699518800280412</v>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>base resize/decode/H2D excluded; actual TTA, aggregation included</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>I03</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>horizontal flip, mean logits</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>/kaggle/working/day2_output/runs/T04/seed0/checkpoint_best.pt</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>0.9772395274298715</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>0.9825764067409312</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>0.01990316115730462</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>10.96094950116822</v>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>11.8326303017966</v>
+      </c>
+      <c r="J5" s="2" t="n">
+        <v>13.64933396074775</v>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>91.23297209730053</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>1.886278530044492</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>base resize/decode/H2D excluded; actual TTA, aggregation included</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>I08</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>single view AMP</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>/kaggle/working/day2_output/runs/T04/seed0/checkpoint_best.pt</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>0.9755872966432046</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>0.9811482433590403</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>0.02042764562329231</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>7.779978001053678</v>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>8.155938750496716</v>
+      </c>
+      <c r="J6" s="2" t="n">
+        <v>8.243153438597801</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>128.5350678195447</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>1.338862610948252</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>base resize/decode/H2D excluded; actual TTA, aggregation included</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>I07</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>temperature scaling on I02; T=0.68002</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>/kaggle/working/day2_output/runs/T04/seed0/checkpoint_best.pt</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>5</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>0.9780877838742277</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>0.9840045701228221</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>0.00364932330644273</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>27.44405200064648</v>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>29.46428734940127</v>
+      </c>
+      <c r="J7" s="2" t="n">
+        <v>30.70588405116723</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>36.43776800803481</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>4.722868767959081</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>base resize/decode/H2D excluded; actual TTA, aggregation included</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:A1"/>
+  <autoFilter ref="A1:M7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -519,7 +1975,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="n"/>
+      <c r="A1" s="5" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:A1"/>
@@ -540,7 +1996,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="n"/>
+      <c r="A1" s="5" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:A1"/>
@@ -554,7 +2010,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -570,59 +2026,539 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>configuration</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>gpu</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>dtype</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>batch</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>bn_fused</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>p50_ms</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>p95_ms</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>p99_ms</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>images_per_s</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>torch</t>
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>I00</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Tesla T4</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>fp32</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" t="b">
+        <v>0</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>5.810885999380844</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>8.823867600040103</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>8.951247469703958</v>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>172.0907964992862</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>2.11.0+cu128</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>I00</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Tesla T4</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>fp32</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>32</v>
+      </c>
+      <c r="E3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>125.6507255020551</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>126.3895896499889</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>126.6205072024604</v>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>254.674215943756</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>2.11.0+cu128</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>I01</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Tesla T4</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>fp32</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>11.09968849959841</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>11.78108184867597</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>12.46520792930823</v>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>90.09261836818033</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>2.11.0+cu128</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>I01</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Tesla T4</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>fp32</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>32</v>
+      </c>
+      <c r="E5" t="b">
+        <v>0</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>249.1046930008451</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>250.4484459985179</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>250.9954487608775</v>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>128.4600447085573</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>2.11.0+cu128</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>I02</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Tesla T4</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>fp32</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="b">
+        <v>0</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>27.3083680003765</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>28.39989105013956</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>29.39391268009785</v>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>36.61881222584275</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>2.11.0+cu128</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>I02</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Tesla T4</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>fp32</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>32</v>
+      </c>
+      <c r="E7" t="b">
+        <v>0</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>623.0854935001844</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>625.3906386493327</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>626.1601704706118</v>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>51.35731827143</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>2.11.0+cu128</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>I03</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Tesla T4</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>fp32</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" t="b">
+        <v>0</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>10.96094950116822</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>11.8326303017966</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>13.64933396074775</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>91.23297209730053</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>2.11.0+cu128</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>I03</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Tesla T4</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>fp32</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>32</v>
+      </c>
+      <c r="E9" t="b">
+        <v>0</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>249.6758359993692</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>251.2519249010438</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>252.0112691898248</v>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>128.1661874562857</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>2.11.0+cu128</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>I08</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Tesla T4</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>amp</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="b">
+        <v>0</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>7.779978001053678</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>8.155938750496716</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>8.243153438597801</v>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>128.5350678195447</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>2.11.0+cu128</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>I08</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Tesla T4</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>amp</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>32</v>
+      </c>
+      <c r="E11" t="b">
+        <v>0</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>47.1123315001023</v>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>48.14107969887118</v>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>48.32303568102361</v>
+      </c>
+      <c r="I11" s="2" t="n">
+        <v>679.2276879765654</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>2.11.0+cu128</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>I07</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Tesla T4</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>fp32</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" t="b">
+        <v>0</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>27.44405200064648</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>29.46428734940127</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>30.70588405116723</v>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>36.43776800803481</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>2.11.0+cu128</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>I07</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Tesla T4</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>fp32</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>32</v>
+      </c>
+      <c r="E13" t="b">
+        <v>0</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>626.7301754996879</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>630.3460168490346</v>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>631.0072944095737</v>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>51.0586553048712</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>2.11.0+cu128</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J1"/>
+  <autoFilter ref="A1:J13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -633,17 +2569,359 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="n"/>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>group</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exp_id</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>configuration</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>macro-F1 val</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>top-1 val</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>latency p95 batch1 (ms)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>params (M)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>GMAC</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Inference</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>I07</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>temperature scaling on I02; T=0.68002</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="n">
+        <v>0.9780877838742277</v>
+      </c>
+      <c r="E2" s="4" t="n">
+        <v>0.9840045701228221</v>
+      </c>
+      <c r="F2" s="4" t="n">
+        <v>29.46428734940127</v>
+      </c>
+      <c r="G2" s="3" t="inlineStr"/>
+      <c r="H2" s="3" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Inference</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>I02</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>five crops, mean probabilities</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>0.9780877838742277</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>0.9840045701228221</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>28.39989105013956</v>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Inference</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>I01</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>horizontal flip, mean probabilities</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>0.9775449072463195</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>0.9828620394173093</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>11.78108184867597</v>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Inference</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>I03</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>horizontal flip, mean logits</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>0.9772395274298715</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>0.9825764067409312</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>11.8326303017966</v>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Inference</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>I00</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>single view</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>0.9755872966432046</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>0.9811482433590403</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>8.823867600040103</v>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Training</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>T04</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>B: Mixup</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>0.9755872966432046</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>0.9811482433590403</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>8.902219451010749</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>27.827049</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>4.454770176</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Inference</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>I08</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>single view AMP</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>0.9755872966432046</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>0.9811482433590403</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>8.155938750496716</v>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Training</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>T05</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>B: CutMix</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>0.9723768356135333</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>0.9791488146243931</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>9.282994750083162</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>27.827049</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>4.454770176</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Training</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>T09</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>F: EMA 0.999</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>0.9713766851027318</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>0.9785775492716366</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>9.28579540195642</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>27.827049</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>4.454770176</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Training</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>T10</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>B+C combination: T04+T06 (chosen on val; may not improve baseline)</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>0.9688417362275819</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>0.9768637532133676</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>8.415209949635027</v>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>27.827049</v>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>4.454770176</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:A1"/>
+  <autoFilter ref="A1:H11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>